--- a/logs/Forward Testing Trade History.xlsx
+++ b/logs/Forward Testing Trade History.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1660,6 +1660,240 @@
         <v>103479</v>
       </c>
     </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07 09:20:02</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59900PE</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>454.45</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07 09:22:15</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>442.75</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>431.73</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>522.62</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>431.73</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>-409.5</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>-459.5</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>15905.75</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>-728</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>103069.5</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07 09:52:01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59900PE</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>454.45</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07 10:15:09</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>431.25</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>431.73</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>522.62</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>431.73</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-812</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>-862</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>15905.75</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>948.5</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>-812</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>102667</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-08 09:20:02</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59800PE</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>433.6</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-08 09:34:41</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>410.5</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>411.92</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>498.64</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>411.92</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>-808.5</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>-858.5</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>15176</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>-808.5</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>102670.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/Forward Testing Trade History.xlsx
+++ b/logs/Forward Testing Trade History.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1894,6 +1894,708 @@
         <v>102670.5</v>
       </c>
     </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-09 09:20:03</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59500PE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>403.95</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-09 10:28:02</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>464.54</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>383.75</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>-764.75</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>-814.75</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>14138.25</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>1891.75</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>-764.75</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>102714.25</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12 09:20:08</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59000PE</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>416.95</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12 09:31:26</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>394.7</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>396.1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>479.49</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>396.1</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-778.75</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>-828.75</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>14593.25</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>549.5</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>-778.75</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>102700.25</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12 09:36:02</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59000PE</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>416.95</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12 10:27:45</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>366.6</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>458.65</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-1762.25</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>-1812.25</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>14593.25</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>211.75</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>-1762.25</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>101716.75</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-13 09:20:02</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59600PE</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>457.15</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-13 09:43:09</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>411.44</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>502.87</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>411.44</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>1604.75</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>1554.75</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>16000.25</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>1604.75</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>-518</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>105083.75</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14 09:20:02</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59600CE</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>607.1</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14 09:23:23</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>573.7</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>576.75</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>637.46</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>576.75</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>-1219</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>21248.5</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>775.25</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>-1169</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>102310</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14 09:37:08</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59600CE</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>607.1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14 09:40:19</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>574.5</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>576.75</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>637.46</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>576.75</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>-1141</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>-1191</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>21248.5</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>-49</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>-1141</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>-5.37</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>102338</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16 09:20:02</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59800CE</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>522.7</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16 09:43:33</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>550.05</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>496.56</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>548.84</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>496.56</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>957.25</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>907.25</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>18294.5</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>957.25</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>-890.75</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>104436.25</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16 10:35:40</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59800CE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>522.7</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16 10:35:51</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>743.2</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>496.56</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>548.84</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>496.56</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>7717.5</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>7667.5</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>18294.5</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>7717.5</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>7717.5</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>42.18</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>111196.5</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-19 09:20:02</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59800PE</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>380.05</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-19 09:58:21</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>418.06</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>342.05</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1370.25</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1320.25</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>13301.75</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>1370.25</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>-575.75</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>101370.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/Forward Testing Trade History.xlsx
+++ b/logs/Forward Testing Trade History.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -440,7 +440,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -2596,6 +2596,2346 @@
         <v>101370.25</v>
       </c>
     </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-20 09:20:02</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59800PE</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-20 09:54:02</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>414.55</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>412.61</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>337.59</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1380.75</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1330.75</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>13128.5</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>1380.75</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>-341.25</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>101380.75</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-21 09:20:03</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59100PE</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>261.05</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-21 09:59:06</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>287.4</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>234.95</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>287.16</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>234.95</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>922.25</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>872.25</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>9136.75</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>922.25</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>-537.25</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>100922.25</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-22 09:20:02</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59300CE</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>400.1</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-22 09:21:05</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>440.11</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>1746.5</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>1696.5</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>14003.5</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>1746.5</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>101746.5</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23 09:35:31</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59100PE</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23 09:45:22</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>294.15</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>237.69</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>290.51</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>237.69</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>1051.75</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>1001.75</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>9243.5</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>1051.75</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>-393.75</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>99912.25</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23 09:35:31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN59100PE</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>264.1</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-23 09:45:22</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>294.15</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>237.69</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>290.51</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>237.69</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1051.75</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>1001.75</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>9243.5</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>1051.75</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>-393.75</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>99912.25</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27 09:20:02</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN58300PE</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>242.95</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27 09:21:58</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>218.66</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>267.25</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>218.66</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>968.5</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>8503.25</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>-442.75</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>100880.75</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27 09:20:02</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JAN58300PE</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>242.95</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27 09:21:59</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>218.66</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>267.25</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>218.66</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>968.5</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>8503.25</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>1018.5</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>-442.75</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>100880.75</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-28 09:20:02</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB59600CE</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1110.75</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-28 11:42:40</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1053.05</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1055.21</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>1166.29</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1055.21</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-2019.5</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-2069.5</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>38876.25</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>864.5</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>-2019.5</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>98811.25</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-29 09:20:02</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB59500CE</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1055.55</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-29 09:50:22</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>1108.9</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1002.77</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1108.33</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1002.77</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1867.25</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>1817.25</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>36944.25</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>1867.25</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>-787.5</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>100628.5</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30 09:20:02</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB59500PE</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>685.85</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-30 09:23:04</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>720.9</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>651.5599999999999</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>720.14</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>651.5599999999999</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>1226.75</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>1176.75</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>24004.75</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>1226.75</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>101805.25</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01 09:40:04</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB59500PE</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>755.1</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-01 09:51:06</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>717.35</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>792.86</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>717.35</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-1928.5</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>-1978.5</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>26428.5</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>-267.75</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>-1928.5</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>99826.75</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02 09:20:02</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB58300CE</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1109.9</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02 09:23:02</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>1165.6</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1054.4</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>1165.39</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1054.4</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1949.5</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>1899.5</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>38846.5</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>1949.5</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U39" s="2" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="V39" s="2" t="n">
+        <v>101726.25</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-03 09:20:02</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60000PE</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>770.05</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-03 09:20:51</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>726.7</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>731.55</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>808.55</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>731.55</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>-1517.25</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>-1567.25</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>26951.75</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>295.75</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>-1517.25</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="U40" s="2" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>100159</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04 09:20:02</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60200CE</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>786.05</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04 09:45:18</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>826</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>746.75</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>825.35</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>746.75</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1398.25</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>1348.25</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>27511.75</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>1398.25</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>-560</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="U41" s="2" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>101507.25</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05 09:20:02</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60200PE</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>629.05</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-05 10:21:57</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>592.9</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>597.6</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>660.5</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>597.6</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-1265.25</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-1315.25</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>22016.75</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>665</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>-1265.25</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="U42" s="2" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>100192</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06 09:20:02</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60100CE</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>708.1</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06 09:38:14</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>671.9</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>672.6900000000001</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>743.51</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>672.6900000000001</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>-1267</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-1317</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>24783.5</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>-1267</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="U43" s="2" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="V43" s="2" t="n">
+        <v>98875</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 09:20:02</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60900CE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>481.65</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 10:28:30</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>432.85</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>433.49</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>529.8200000000001</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>433.49</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-1708</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-1758</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>16857.75</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>-10.13</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>665</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>-1708</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>-10.13</v>
+      </c>
+      <c r="U44" s="2" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>97117</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-10 09:20:02</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60800CE</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>512.25</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-10 11:37:21</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>486.64</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>537.86</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>486.64</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-932.75</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>-982.75</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>17928.75</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>516.25</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>-932.75</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="U45" s="2" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>96134.25</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11 09:20:02</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60500PE</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>393.45</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-11 09:40:05</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>435.1</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>354.11</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>432.8</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>354.11</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>1457.75</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>1407.75</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>13770.75</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>1457.75</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>-117.25</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="U46" s="2" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="V46" s="2" t="n">
+        <v>97542</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12 09:20:02</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60800CE</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>455.65</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-12 10:14:07</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>504</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>410.09</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>501.22</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>410.09</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1692.25</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>1642.25</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>15947.75</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>1692.25</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U47" s="2" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="V47" s="2" t="n">
+        <v>99184.25</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13 09:20:02</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB60400PE</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13 10:15:05</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>405.15</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>405.08</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>1291.5</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>1241.5</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>12888.75</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>1291.5</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>-390.25</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="U48" s="2" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="V48" s="2" t="n">
+        <v>100425.75</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18 09:20:02</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB61300CE</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>308.2</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18 09:56:04</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>273.9</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>277.38</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>277.38</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-1200.5</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-1250.5</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>10787</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>-11.13</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>1036</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>-1200.5</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>-11.13</v>
+      </c>
+      <c r="U49" s="2" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>99175.25</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-23 09:26:35</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26FEB61300CE</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>297.1</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-23 09:26:46</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>267.39</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>326.81</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>267.39</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1897</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>1847</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>10398.5</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>1897</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>1897</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="U50" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="V50" s="2" t="n">
+        <v>101022.25</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:20:02</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR61300CE</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1044.35</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:53:41</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>986.3</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>992.13</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>1096.57</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>992.13</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>-2031.75</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-2081.75</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>36552.25</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>582.75</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>-2031.75</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="U51" s="2" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="V51" s="2" t="n">
+        <v>98940.5</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:20:02</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR61100PE</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>698.9</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-26 09:36:51</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>662</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>663.95</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>733.85</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>663.95</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-1291.5</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>-1341.5</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>24461.5</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>-1291.5</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="U52" s="2" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="V52" s="2" t="n">
+        <v>97599</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-27 09:20:02</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR60900PE</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>675.1</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-27 09:36:32</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>709</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>641.35</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>708.86</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>641.35</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>1186.5</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>1136.5</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>23628.5</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>1186.5</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U53" s="2" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>98735.5</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:24:21</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR60100CE</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1132.9</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-02 09:28:55</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>1193</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1076.25</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>1189.54</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1076.25</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>2103.5</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>2053.5</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>39651.5</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>2103.5</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>-441</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="U54" s="2" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="V54" s="2" t="n">
+        <v>100789</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:20:02</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR58800PE</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>990.05</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-05 14:24:53</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>901.25</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>940.55</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>1039.55</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>940.55</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-3108</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>-3158</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>34651.75</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>995.75</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>-3108</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="U55" s="2" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="V55" s="2" t="n">
+        <v>97631</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-06 09:20:02</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR58500PE</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>853.1</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-06 09:35:06</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>810.4400000000001</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>895.76</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>810.4400000000001</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>1606.5</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>1556.5</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>29858.5</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>1606.5</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>-539</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="U56" s="2" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>99187.5</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:43:40</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR55500PE</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1340.1</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:43:50</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>1437.3</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>1273.09</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>1407.11</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1273.09</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>3402</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>3352</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>46903.5</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>3402</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>3402</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="U57" s="2" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>102539.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/Forward Testing Trade History.xlsx
+++ b/logs/Forward Testing Trade History.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4936,6 +4936,1020 @@
         <v>102539.5</v>
       </c>
     </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12 09:20:02</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR55100CE</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1271.95</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12 09:51:50</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1365</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>1182.91</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>1360.99</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1182.91</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>3256.75</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>3206.75</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>44518.25</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>3256.75</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>-145.25</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="U58" s="2" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="V58" s="2" t="n">
+        <v>105746.25</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12 14:45:31</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR55100CE</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1271.95</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12 14:45:41</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1385.8</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>1182.91</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>1360.99</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1182.91</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>3984.75</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>3934.75</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>44518.25</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>3984.75</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>3984.75</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="U59" s="2" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="V59" s="2" t="n">
+        <v>109681</v>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13 09:20:02</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR54500PE</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1077.7</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13 09:46:15</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>1155</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>1002.26</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>1153.14</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1002.26</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>2705.5</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>2655.5</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>37719.5</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="Q60" s="2" t="n">
+        <v>2705.5</v>
+      </c>
+      <c r="R60" s="2" t="n">
+        <v>-1123.5</v>
+      </c>
+      <c r="S60" s="2" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>-2.98</v>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>112336.5</v>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 09:20:02</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR53900CE</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1326.95</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 09:42:31</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1420</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1234.06</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>1419.84</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1234.06</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>3256.75</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>3206.75</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>46443.25</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="Q61" s="2" t="n">
+        <v>3256.75</v>
+      </c>
+      <c r="R61" s="2" t="n">
+        <v>-232.75</v>
+      </c>
+      <c r="S61" s="2" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="T61" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U61" s="2" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>115543.25</v>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 09:20:02</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR54200PE</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>991.15</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 09:37:03</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>919.6</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>921.77</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>1060.53</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>921.77</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-2504.25</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>-2554.25</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>34690.25</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="Q62" s="2" t="n">
+        <v>1683.5</v>
+      </c>
+      <c r="R62" s="2" t="n">
+        <v>-2504.25</v>
+      </c>
+      <c r="S62" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="T62" s="2" t="n">
+        <v>-7.22</v>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="V62" s="2" t="n">
+        <v>112989</v>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19 09:20:02</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR53400PE</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>730.15</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19 09:22:25</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>678.55</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>679.04</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>781.26</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>679.04</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-1806</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>-1856</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>25555.25</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="Q63" s="2" t="n">
+        <v>637</v>
+      </c>
+      <c r="R63" s="2" t="n">
+        <v>-1806</v>
+      </c>
+      <c r="S63" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>-7.07</v>
+      </c>
+      <c r="U63" s="2" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>111133</v>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20 09:20:02</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR54200CE</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>1010.1</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-20 09:32:53</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1093.25</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>939.39</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>1080.81</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>939.39</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>2910.25</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>2860.25</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>35353.5</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="Q64" s="2" t="n">
+        <v>2910.25</v>
+      </c>
+      <c r="R64" s="2" t="n">
+        <v>-2411.5</v>
+      </c>
+      <c r="S64" s="2" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>113993.25</v>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23 09:20:02</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR52100PE</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>979.95</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23 09:50:34</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1049.1</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>911.35</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>1048.55</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>911.35</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>2420.25</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>2370.25</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>34298.25</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="Q65" s="2" t="n">
+        <v>2420.25</v>
+      </c>
+      <c r="R65" s="2" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="S65" s="2" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="T65" s="2" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="U65" s="2" t="n">
+        <v>25.66</v>
+      </c>
+      <c r="V65" s="2" t="n">
+        <v>116363.5</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:20:02</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR52500CE</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>880.5</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:31:22</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>942.4</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>818.86</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>942.14</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>818.86</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>2166.5</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>2116.5</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>30817.5</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="Q66" s="2" t="n">
+        <v>2166.5</v>
+      </c>
+      <c r="R66" s="2" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="S66" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="V66" s="2" t="n">
+        <v>118480</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:22:05</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR53500CE</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>748.1</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:25:25</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>695.73</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>800.47</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>695.73</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>1851.5</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>1801.5</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>26183.5</v>
+      </c>
+      <c r="P67" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="Q67" s="2" t="n">
+        <v>1851.5</v>
+      </c>
+      <c r="R67" s="2" t="n">
+        <v>-243.25</v>
+      </c>
+      <c r="S67" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="T67" s="2" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="U67" s="2" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="V67" s="2" t="n">
+        <v>120281.5</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:25:46</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR52800PE</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>593.1</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:30:12</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>644.15</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>551.58</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>634.62</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>551.58</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>1786.75</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>1736.75</v>
+      </c>
+      <c r="O68" s="2" t="n">
+        <v>20758.5</v>
+      </c>
+      <c r="P68" s="2" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="Q68" s="2" t="n">
+        <v>1786.75</v>
+      </c>
+      <c r="R68" s="2" t="n">
+        <v>-152.25</v>
+      </c>
+      <c r="S68" s="2" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="T68" s="2" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>122018.25</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:20:02</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAR51000PE</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:28:20</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>297.45</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>297.53</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>378.67</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>297.53</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-1422.75</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-1472.75</v>
+      </c>
+      <c r="O69" s="2" t="n">
+        <v>11833.5</v>
+      </c>
+      <c r="P69" s="2" t="n">
+        <v>-12.02</v>
+      </c>
+      <c r="Q69" s="2" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="R69" s="2" t="n">
+        <v>-1422.75</v>
+      </c>
+      <c r="S69" s="2" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T69" s="2" t="n">
+        <v>-12.02</v>
+      </c>
+      <c r="U69" s="2" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="V69" s="2" t="n">
+        <v>120545.5</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 09:20:02</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR51400PE</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>1443.9</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01 10:25:06</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1551.3</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>1342.83</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>1544.97</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>1342.83</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>3759</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>3709</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>50536.5</v>
+      </c>
+      <c r="P70" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="Q70" s="2" t="n">
+        <v>3759</v>
+      </c>
+      <c r="R70" s="2" t="n">
+        <v>-2310</v>
+      </c>
+      <c r="S70" s="2" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="V70" s="2" t="n">
+        <v>124254.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/Forward Testing Trade History.xlsx
+++ b/logs/Forward Testing Trade History.xlsx
@@ -2,35 +2,192 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="8520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -39,12 +196,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -52,9 +395,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -65,8 +650,56 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,7 +1052,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -429,8 +1061,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:V73"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -444,13 +1076,13 @@
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="14"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="8" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
@@ -634,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.503006012024048</v>
+        <v>1.50300601202405</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -5948,6 +6580,186 @@
       </c>
       <c r="V70" s="2" t="n">
         <v>124254.5</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="n"/>
+      <c r="Q71" s="2" t="n"/>
+      <c r="R71" s="2" t="n"/>
+      <c r="S71" s="2" t="n"/>
+      <c r="T71" s="2" t="n"/>
+      <c r="U71" s="2" t="n"/>
+      <c r="V71" s="2" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06 09:20:02</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR51800CE</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>1729.9</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-06 09:48:41</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>1604.1</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>1608.81</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>1850.99</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>1608.81</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-4403</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>-4453</v>
+      </c>
+      <c r="O72" s="2" t="n">
+        <v>60546.5</v>
+      </c>
+      <c r="P72" s="2" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="Q72" s="2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="R72" s="2" t="n">
+        <v>-4403</v>
+      </c>
+      <c r="S72" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T72" s="2" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>119751.5</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07 09:20:02</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR51900PE</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>1452.6</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-07 09:27:27</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1350.05</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>1350.92</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>1554.28</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1350.92</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-3589.25</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-3639.25</v>
+      </c>
+      <c r="O73" s="2" t="n">
+        <v>50841</v>
+      </c>
+      <c r="P73" s="2" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="Q73" s="2" t="n">
+        <v>677.25</v>
+      </c>
+      <c r="R73" s="2" t="n">
+        <v>-3589.25</v>
+      </c>
+      <c r="S73" s="2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T73" s="2" t="n">
+        <v>-7.06</v>
+      </c>
+      <c r="U73" s="2" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>116112.25</v>
       </c>
     </row>
   </sheetData>

--- a/logs/Forward Testing Trade History.xlsx
+++ b/logs/Forward Testing Trade History.xlsx
@@ -1061,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6762,6 +6762,5466 @@
         <v>116112.25</v>
       </c>
     </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 09:20:03</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR55200CE</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>1133.3</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 09:24:51</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1052.85</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1053.97</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>1212.63</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1053.97</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-2815.75</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>-2865.75</v>
+      </c>
+      <c r="O74" s="2" t="n">
+        <v>39665.5</v>
+      </c>
+      <c r="P74" s="2" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="Q74" s="2" t="n">
+        <v>1422.75</v>
+      </c>
+      <c r="R74" s="2" t="n">
+        <v>-2815.75</v>
+      </c>
+      <c r="S74" s="2" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="T74" s="2" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="U74" s="2" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="V74" s="2" t="n">
+        <v>113246.5</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09 09:20:03</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR55200PE</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>946.7</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-09 09:42:53</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>1013.7</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>880.4299999999999</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>1012.97</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>880.4299999999999</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>2345</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>2295</v>
+      </c>
+      <c r="O75" s="2" t="n">
+        <v>33134.5</v>
+      </c>
+      <c r="P75" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="Q75" s="2" t="n">
+        <v>2345</v>
+      </c>
+      <c r="R75" s="2" t="n">
+        <v>-234.5</v>
+      </c>
+      <c r="S75" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="U75" s="2" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>115541.5</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10 09:20:03</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR55600CE</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>1109.45</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10 09:31:08</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>1188.8</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1031.79</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>1187.11</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>1031.79</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>2777.25</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>2727.25</v>
+      </c>
+      <c r="O76" s="2" t="n">
+        <v>38830.75</v>
+      </c>
+      <c r="P76" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="Q76" s="2" t="n">
+        <v>2777.25</v>
+      </c>
+      <c r="R76" s="2" t="n">
+        <v>-805</v>
+      </c>
+      <c r="S76" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="U76" s="2" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>118268.75</v>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 09:20:03</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR54800CE</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>1092.9</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 09:53:22</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>1016.4</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1169.4</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>1016.4</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>2712.5</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>2662.5</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>38251.5</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="Q77" s="2" t="n">
+        <v>2712.5</v>
+      </c>
+      <c r="R77" s="2" t="n">
+        <v>-1002.75</v>
+      </c>
+      <c r="S77" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="T77" s="2" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="U77" s="2" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>120931.25</v>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16 09:21:50</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR56500PE</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>859.1</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16 11:45:54</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>920.65</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>798.96</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>919.24</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>798.96</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>2154.25</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>2104.25</v>
+      </c>
+      <c r="O78" s="2" t="n">
+        <v>30068.5</v>
+      </c>
+      <c r="P78" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="Q78" s="2" t="n">
+        <v>2154.25</v>
+      </c>
+      <c r="R78" s="2" t="n">
+        <v>-316.75</v>
+      </c>
+      <c r="S78" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="T78" s="2" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="U78" s="2" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="V78" s="2" t="n">
+        <v>123035.5</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 09:20:03</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR56200CE</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 10:26:25</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>942.8</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>818.4</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>941.6</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>818.4</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>2198</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>2148</v>
+      </c>
+      <c r="O79" s="2" t="n">
+        <v>30800</v>
+      </c>
+      <c r="P79" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="Q79" s="2" t="n">
+        <v>2198</v>
+      </c>
+      <c r="R79" s="2" t="n">
+        <v>-1853.25</v>
+      </c>
+      <c r="S79" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="T79" s="2" t="n">
+        <v>-6.02</v>
+      </c>
+      <c r="U79" s="2" t="n">
+        <v>17.81</v>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>102148</v>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:20:02</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR56800CE</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>780.1</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:32:52</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>714</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>725.49</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>834.71</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>725.49</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-2313.5</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>-2363.5</v>
+      </c>
+      <c r="O80" s="2" t="n">
+        <v>27303.5</v>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="Q80" s="2" t="n">
+        <v>1326.5</v>
+      </c>
+      <c r="R80" s="2" t="n">
+        <v>-2313.5</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>-8.470000000000001</v>
+      </c>
+      <c r="U80" s="2" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="V80" s="2" t="n">
+        <v>99784.5</v>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 09:20:02</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR57000CE</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>700.1</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 09:34:32</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>751.15</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>651.09</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>749.11</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>651.09</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1786.75</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>1736.75</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>24503.5</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>1786.75</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>-71.75</v>
+      </c>
+      <c r="S81" s="2" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="T81" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="U81" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>101521.25</v>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22 09:20:02</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR57100PE</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>700.1</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:15:51</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>648</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>651.09</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>749.11</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>651.09</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1823.5</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-1873.5</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>24503.5</v>
+      </c>
+      <c r="P82" s="2" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="Q82" s="2" t="n">
+        <v>274.75</v>
+      </c>
+      <c r="R82" s="2" t="n">
+        <v>-1823.5</v>
+      </c>
+      <c r="S82" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T82" s="2" t="n">
+        <v>-7.44</v>
+      </c>
+      <c r="U82" s="2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>99647.75</v>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 09:20:02</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR56700CE</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>649.5</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23 10:07:52</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>603.2</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>604.03</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>694.97</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>604.03</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1620.5</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-1670.5</v>
+      </c>
+      <c r="O83" s="2" t="n">
+        <v>22732.5</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="Q83" s="2" t="n">
+        <v>463.75</v>
+      </c>
+      <c r="R83" s="2" t="n">
+        <v>-1620.5</v>
+      </c>
+      <c r="S83" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T83" s="2" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="U83" s="2" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="V83" s="2" t="n">
+        <v>97977.25</v>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24 09:20:02</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR56200PE</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>506.95</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24 09:40:09</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>471.46</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>542.4400000000001</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>471.46</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>1506.75</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>1456.75</v>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v>17743.25</v>
+      </c>
+      <c r="P84" s="2" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>1506.75</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>-519.75</v>
+      </c>
+      <c r="S84" s="2" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="T84" s="2" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="U84" s="2" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>99434</v>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:20:02</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26APR56000CE</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>215.1</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:35:30</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>189.29</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>240.91</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>189.29</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1053.5</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-1103.5</v>
+      </c>
+      <c r="O85" s="2" t="n">
+        <v>7528.5</v>
+      </c>
+      <c r="P85" s="2" t="n">
+        <v>-13.99</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>-1053.5</v>
+      </c>
+      <c r="S85" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="T85" s="2" t="n">
+        <v>-13.99</v>
+      </c>
+      <c r="U85" s="2" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>98330.5</v>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:20:02</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY55400PE</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>1056.9</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:44:11</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>981.3</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>982.92</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>1130.88</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>982.92</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-2646</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-2696</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>36991.5</v>
+      </c>
+      <c r="P86" s="2" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>432.25</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>-2646</v>
+      </c>
+      <c r="S86" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="U86" s="2" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>95634.5</v>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:20:02</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY54600PE</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>1050.1</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30 09:29:14</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>1127.25</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>976.59</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>1123.61</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>976.59</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>2700.25</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>2650.25</v>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>36753.5</v>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="Q87" s="2" t="n">
+        <v>2700.25</v>
+      </c>
+      <c r="R87" s="2" t="n">
+        <v>-686</v>
+      </c>
+      <c r="S87" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="T87" s="2" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="U87" s="2" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>98284.75</v>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 09:20:03</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY54400PE</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>957.45</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-05 10:59:12</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>1024.5</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>890.4299999999999</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>1024.47</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>890.4299999999999</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>2346.75</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>2296.75</v>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v>33510.75</v>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>2346.75</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>-1522.5</v>
+      </c>
+      <c r="S88" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T88" s="2" t="n">
+        <v>-4.54</v>
+      </c>
+      <c r="U88" s="2" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="V88" s="2" t="n">
+        <v>100581.5</v>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 09:20:02</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY55100PE</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>900.15</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-06 10:19:54</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>836.1</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>837.14</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>963.16</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>837.14</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-2241.75</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-2291.75</v>
+      </c>
+      <c r="O89" s="2" t="n">
+        <v>31505.25</v>
+      </c>
+      <c r="P89" s="2" t="n">
+        <v>-7.12</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>344.75</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>-2241.75</v>
+      </c>
+      <c r="S89" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T89" s="2" t="n">
+        <v>-7.12</v>
+      </c>
+      <c r="U89" s="2" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="V89" s="2" t="n">
+        <v>98289.75</v>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 09:20:02</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY55800PE</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>781.1</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 09:38:01</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>724.55</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>726.42</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>835.78</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>726.42</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1979.25</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-2029.25</v>
+      </c>
+      <c r="O90" s="2" t="n">
+        <v>27338.5</v>
+      </c>
+      <c r="P90" s="2" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="Q90" s="2" t="n">
+        <v>1541.75</v>
+      </c>
+      <c r="R90" s="2" t="n">
+        <v>-1979.25</v>
+      </c>
+      <c r="S90" s="2" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="T90" s="2" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="U90" s="2" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="V90" s="2" t="n">
+        <v>96260.5</v>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 09:20:02</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY55500PE</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>827.1</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-08 10:23:51</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>766</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>769.2</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>769.2</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-2138.5</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-2188.5</v>
+      </c>
+      <c r="O91" s="2" t="n">
+        <v>28948.5</v>
+      </c>
+      <c r="P91" s="2" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>689.5</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>-2138.5</v>
+      </c>
+      <c r="S91" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T91" s="2" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="U91" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>94072</v>
+      </c>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11 09:20:03</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY54600PE</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>890.05</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11 09:24:02</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>827.75</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>952.35</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>827.75</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-2416.75</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-2466.75</v>
+      </c>
+      <c r="O92" s="2" t="n">
+        <v>31151.75</v>
+      </c>
+      <c r="P92" s="2" t="n">
+        <v>-7.76</v>
+      </c>
+      <c r="Q92" s="2" t="n">
+        <v>-162.75</v>
+      </c>
+      <c r="R92" s="2" t="n">
+        <v>-2416.75</v>
+      </c>
+      <c r="S92" s="2" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="T92" s="2" t="n">
+        <v>-7.76</v>
+      </c>
+      <c r="U92" s="2" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>91605.25</v>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12 09:20:02</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY54200PE</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>966.05</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12 09:53:20</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>896.95</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>898.4299999999999</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>1033.67</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>898.4299999999999</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-2418.5</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-2468.5</v>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>33811.75</v>
+      </c>
+      <c r="P93" s="2" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>878.5</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>-2418.5</v>
+      </c>
+      <c r="S93" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T93" s="2" t="n">
+        <v>-7.15</v>
+      </c>
+      <c r="U93" s="2" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="V93" s="2" t="n">
+        <v>89136.75</v>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:20:02</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY53600PE</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>904</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13 09:24:57</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>838</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>840.72</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>967.28</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>840.72</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-2310</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-2360</v>
+      </c>
+      <c r="O94" s="2" t="n">
+        <v>31640</v>
+      </c>
+      <c r="P94" s="2" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="Q94" s="2" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="R94" s="2" t="n">
+        <v>-2310</v>
+      </c>
+      <c r="S94" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T94" s="2" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="U94" s="2" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>86776.75</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14 09:20:02</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY53900CE</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>939.75</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14 09:40:06</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>873.05</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>873.97</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1005.53</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>873.97</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-2334.5</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-2384.5</v>
+      </c>
+      <c r="O95" s="2" t="n">
+        <v>32891.25</v>
+      </c>
+      <c r="P95" s="2" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="Q95" s="2" t="n">
+        <v>1561</v>
+      </c>
+      <c r="R95" s="2" t="n">
+        <v>-2334.5</v>
+      </c>
+      <c r="S95" s="2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T95" s="2" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="U95" s="2" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="V95" s="2" t="n">
+        <v>84392.25</v>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:20:02</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY54300CE</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>828.45</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:42:28</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>889.2</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>770.46</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>886.4400000000001</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>770.46</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>2126.25</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>2076.25</v>
+      </c>
+      <c r="O96" s="2" t="n">
+        <v>28995.75</v>
+      </c>
+      <c r="P96" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="Q96" s="2" t="n">
+        <v>2126.25</v>
+      </c>
+      <c r="R96" s="2" t="n">
+        <v>-1345.75</v>
+      </c>
+      <c r="S96" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="T96" s="2" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="U96" s="2" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>86468.5</v>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 09:20:02</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY53500PE</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>646.05</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-19 09:26:17</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>600.7</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>600.83</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>691.27</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>600.83</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1587.25</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-1637.25</v>
+      </c>
+      <c r="O97" s="2" t="n">
+        <v>22611.75</v>
+      </c>
+      <c r="P97" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="Q97" s="2" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="R97" s="2" t="n">
+        <v>-1587.25</v>
+      </c>
+      <c r="S97" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T97" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="U97" s="2" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="V97" s="2" t="n">
+        <v>84831.25</v>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 09:20:02</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY53000CE</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>709.25</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 10:02:44</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>657.25</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>659.6</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>758.9</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>659.6</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1820</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-1870</v>
+      </c>
+      <c r="O98" s="2" t="n">
+        <v>24823.75</v>
+      </c>
+      <c r="P98" s="2" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="Q98" s="2" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="R98" s="2" t="n">
+        <v>-1820</v>
+      </c>
+      <c r="S98" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T98" s="2" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="U98" s="2" t="n">
+        <v>19.22</v>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>82961.25</v>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:20:02</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY53800PE</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>502.1</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 09:22:10</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>462.55</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>466.95</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>537.25</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>466.95</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1384.25</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-1434.25</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>17573.5</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="Q99" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R99" s="2" t="n">
+        <v>-1384.25</v>
+      </c>
+      <c r="S99" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="T99" s="2" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="U99" s="2" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="V99" s="2" t="n">
+        <v>81527</v>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:20:02</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY53700CE</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>506.15</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 09:21:45</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>542.5</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>470.72</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>541.58</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>470.72</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>1272.25</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>1222.25</v>
+      </c>
+      <c r="O100" s="2" t="n">
+        <v>17715.25</v>
+      </c>
+      <c r="P100" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="Q100" s="2" t="n">
+        <v>1272.25</v>
+      </c>
+      <c r="R100" s="2" t="n">
+        <v>250.25</v>
+      </c>
+      <c r="S100" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="T100" s="2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U100" s="2" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="V100" s="2" t="n">
+        <v>82749.25</v>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 09:20:02</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY54900CE</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>330.85</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25 10:04:20</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>291.15</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>370.55</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>291.15</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>1436.75</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>1386.75</v>
+      </c>
+      <c r="O101" s="2" t="n">
+        <v>11579.75</v>
+      </c>
+      <c r="P101" s="2" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="Q101" s="2" t="n">
+        <v>1436.75</v>
+      </c>
+      <c r="R101" s="2" t="n">
+        <v>-925.75</v>
+      </c>
+      <c r="S101" s="2" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="T101" s="2" t="n">
+        <v>-7.99</v>
+      </c>
+      <c r="U101" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>84136</v>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:20:02</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26MAY55400CE</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>215.7</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-26 09:38:47</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>242.15</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>189.82</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>241.58</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>189.82</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>925.75</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>875.75</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>7549.5</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="Q102" s="2" t="n">
+        <v>925.75</v>
+      </c>
+      <c r="R102" s="2" t="n">
+        <v>418.25</v>
+      </c>
+      <c r="S102" s="2" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="T102" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="U102" s="2" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="V102" s="2" t="n">
+        <v>85011.75</v>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27 09:20:02</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN55100CE</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>1372.05</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27 10:48:07</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>1275.5</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>1276.01</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1468.09</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>1276.01</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-3379.25</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-3429.25</v>
+      </c>
+      <c r="O103" s="2" t="n">
+        <v>48021.75</v>
+      </c>
+      <c r="P103" s="2" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="Q103" s="2" t="n">
+        <v>978.25</v>
+      </c>
+      <c r="R103" s="2" t="n">
+        <v>-3379.25</v>
+      </c>
+      <c r="S103" s="2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T103" s="2" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="U103" s="2" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="V103" s="2" t="n">
+        <v>81582.5</v>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:20:03</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN55100CE</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>1292.65</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29 09:28:46</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>1197.7</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>1202.16</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>1383.14</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>1202.16</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-3323.25</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-3373.25</v>
+      </c>
+      <c r="O104" s="2" t="n">
+        <v>45242.75</v>
+      </c>
+      <c r="P104" s="2" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="Q104" s="2" t="n">
+        <v>539</v>
+      </c>
+      <c r="R104" s="2" t="n">
+        <v>-3323.25</v>
+      </c>
+      <c r="S104" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="T104" s="2" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="U104" s="2" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="V104" s="2" t="n">
+        <v>78209.25</v>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01 09:20:02</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN54200PE</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>1050.7</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01 10:24:34</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>1129.4</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>977.15</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1124.25</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>977.15</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>2754.5</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>2704.5</v>
+      </c>
+      <c r="O105" s="2" t="n">
+        <v>36774.5</v>
+      </c>
+      <c r="P105" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="Q105" s="2" t="n">
+        <v>2754.5</v>
+      </c>
+      <c r="R105" s="2" t="n">
+        <v>-211.75</v>
+      </c>
+      <c r="S105" s="2" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="T105" s="2" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="U105" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="V105" s="2" t="n">
+        <v>80913.75</v>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02 09:20:02</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN53400CE</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>1220.05</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02 09:39:27</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>1306.45</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>1134.65</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1305.45</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1134.65</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>3024</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>2974</v>
+      </c>
+      <c r="O106" s="2" t="n">
+        <v>42701.75</v>
+      </c>
+      <c r="P106" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="Q106" s="2" t="n">
+        <v>3024</v>
+      </c>
+      <c r="R106" s="2" t="n">
+        <v>-1015</v>
+      </c>
+      <c r="S106" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="U106" s="2" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="V106" s="2" t="n">
+        <v>83887.75</v>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:20:02</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN53200PE</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>960.1</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:46:27</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>1027.75</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>892.89</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1027.31</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>892.89</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>2367.75</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>2317.75</v>
+      </c>
+      <c r="O107" s="2" t="n">
+        <v>33603.5</v>
+      </c>
+      <c r="P107" s="2" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="Q107" s="2" t="n">
+        <v>2367.75</v>
+      </c>
+      <c r="R107" s="2" t="n">
+        <v>-808.5</v>
+      </c>
+      <c r="S107" s="2" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="U107" s="2" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="V107" s="2" t="n">
+        <v>86205.5</v>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:20:03</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN54100CE</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>1272.05</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04 09:57:09</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>1379.15</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>1183.01</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>1361.09</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>1183.01</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>3748.5</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>3698.5</v>
+      </c>
+      <c r="O108" s="2" t="n">
+        <v>44521.75</v>
+      </c>
+      <c r="P108" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="Q108" s="2" t="n">
+        <v>3748.5</v>
+      </c>
+      <c r="R108" s="2" t="n">
+        <v>-642.25</v>
+      </c>
+      <c r="S108" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="U108" s="2" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>89904</v>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 09:20:02</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN54300PE</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>954.45</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05 09:30:33</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>883.05</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>887.64</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1021.26</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>887.64</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-2549</v>
+      </c>
+      <c r="O109" s="2" t="n">
+        <v>33405.75</v>
+      </c>
+      <c r="P109" s="2" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="Q109" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="R109" s="2" t="n">
+        <v>-2499</v>
+      </c>
+      <c r="S109" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="T109" s="2" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="U109" s="2" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="V109" s="2" t="n">
+        <v>87355</v>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 09:20:03</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN54200CE</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>1239.2</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 09:31:04</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>1330</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>1152.46</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>1325.94</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1152.46</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>3178</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>3128</v>
+      </c>
+      <c r="O110" s="2" t="n">
+        <v>43372</v>
+      </c>
+      <c r="P110" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="Q110" s="2" t="n">
+        <v>3178</v>
+      </c>
+      <c r="R110" s="2" t="n">
+        <v>-334.25</v>
+      </c>
+      <c r="S110" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="T110" s="2" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="U110" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="V110" s="2" t="n">
+        <v>90483</v>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:20:02</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN54500CE</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>1125.1</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09 09:21:21</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>1204.75</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>1046.34</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1203.86</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1046.34</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>2787.75</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>2737.75</v>
+      </c>
+      <c r="O111" s="2" t="n">
+        <v>39378.5</v>
+      </c>
+      <c r="P111" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="Q111" s="2" t="n">
+        <v>2787.75</v>
+      </c>
+      <c r="R111" s="2" t="n">
+        <v>659.75</v>
+      </c>
+      <c r="S111" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="T111" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U111" s="2" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="V111" s="2" t="n">
+        <v>93220.75</v>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 09:20:02</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN55400CE</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:43:00</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>963.75</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>967.2</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1112.8</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>967.2</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-2668.75</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-2718.75</v>
+      </c>
+      <c r="O112" s="2" t="n">
+        <v>36400</v>
+      </c>
+      <c r="P112" s="2" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="Q112" s="2" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R112" s="2" t="n">
+        <v>-2668.75</v>
+      </c>
+      <c r="S112" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T112" s="2" t="n">
+        <v>-7.33</v>
+      </c>
+      <c r="U112" s="2" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="V112" s="2" t="n">
+        <v>90502</v>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:20:02</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN55000CE</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>984.1</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:44:02</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>915.21</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1052.99</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>915.21</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>2446.5</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>2396.5</v>
+      </c>
+      <c r="O113" s="2" t="n">
+        <v>34443.5</v>
+      </c>
+      <c r="P113" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q113" s="2" t="n">
+        <v>2446.5</v>
+      </c>
+      <c r="R113" s="2" t="n">
+        <v>-638.75</v>
+      </c>
+      <c r="S113" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="T113" s="2" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="U113" s="2" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="V113" s="2" t="n">
+        <v>92898.5</v>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12 09:21:33</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN55800PE</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>824.05</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:17:06</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>882.3</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>766.37</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>881.73</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>766.37</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>2038.75</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>1988.75</v>
+      </c>
+      <c r="O114" s="2" t="n">
+        <v>28841.75</v>
+      </c>
+      <c r="P114" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="Q114" s="2" t="n">
+        <v>2038.75</v>
+      </c>
+      <c r="R114" s="2" t="n">
+        <v>-175</v>
+      </c>
+      <c r="S114" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="T114" s="2" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="U114" s="2" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="V114" s="2" t="n">
+        <v>94887.25</v>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15 09:20:02</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN57500PE</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>793.95</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15 10:07:24</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>852.8</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>738.37</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>849.53</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>738.37</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>2059.75</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>2009.75</v>
+      </c>
+      <c r="O115" s="2" t="n">
+        <v>27788.25</v>
+      </c>
+      <c r="P115" s="2" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="Q115" s="2" t="n">
+        <v>2059.75</v>
+      </c>
+      <c r="R115" s="2" t="n">
+        <v>-311.5</v>
+      </c>
+      <c r="S115" s="2" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="T115" s="2" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="U115" s="2" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="V115" s="2" t="n">
+        <v>96897</v>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:20:02</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN57200PE</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>749.2</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:56:23</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>696.75</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>696.76</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>801.64</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>696.76</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1835.75</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-1885.75</v>
+      </c>
+      <c r="O116" s="2" t="n">
+        <v>26222</v>
+      </c>
+      <c r="P116" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Q116" s="2" t="n">
+        <v>267.75</v>
+      </c>
+      <c r="R116" s="2" t="n">
+        <v>-1835.75</v>
+      </c>
+      <c r="S116" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T116" s="2" t="n">
+        <v>-7</v>
+      </c>
+      <c r="U116" s="2" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="V116" s="2" t="n">
+        <v>95011.25</v>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:20:02</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN57200PE</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>645.7</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17 09:43:27</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>600.4</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>600.5</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>690.9</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>600.5</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1585.5</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-1635.5</v>
+      </c>
+      <c r="O117" s="2" t="n">
+        <v>22599.5</v>
+      </c>
+      <c r="P117" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="Q117" s="2" t="n">
+        <v>432.25</v>
+      </c>
+      <c r="R117" s="2" t="n">
+        <v>-1585.5</v>
+      </c>
+      <c r="S117" s="2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T117" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="U117" s="2" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="V117" s="2" t="n">
+        <v>93375.75</v>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 09:21:57</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN57600PE</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>473.3</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 10:54:16</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>532.6</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>530.1</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>2075.5</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>2025.5</v>
+      </c>
+      <c r="O118" s="2" t="n">
+        <v>16565.5</v>
+      </c>
+      <c r="P118" s="2" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="Q118" s="2" t="n">
+        <v>2075.5</v>
+      </c>
+      <c r="R118" s="2" t="n">
+        <v>-413</v>
+      </c>
+      <c r="S118" s="2" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="T118" s="2" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="U118" s="2" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="V118" s="2" t="n">
+        <v>95401.25</v>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 09:20:02</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN57800PE</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>429.9</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:30:12</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>481.49</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>378.31</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1835.75</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-1885.75</v>
+      </c>
+      <c r="O119" s="2" t="n">
+        <v>15046.5</v>
+      </c>
+      <c r="P119" s="2" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="Q119" s="2" t="n">
+        <v>166.25</v>
+      </c>
+      <c r="R119" s="2" t="n">
+        <v>-1835.75</v>
+      </c>
+      <c r="S119" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T119" s="2" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="U119" s="2" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="V119" s="2" t="n">
+        <v>93515.5</v>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 09:20:02</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN57800PE</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 11:46:00</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>424</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>330.09</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>420.11</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>330.09</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>1711.5</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>1661.5</v>
+      </c>
+      <c r="O120" s="2" t="n">
+        <v>13128.5</v>
+      </c>
+      <c r="P120" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="Q120" s="2" t="n">
+        <v>1711.5</v>
+      </c>
+      <c r="R120" s="2" t="n">
+        <v>-315</v>
+      </c>
+      <c r="S120" s="2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="T120" s="2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="U120" s="2" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V120" s="2" t="n">
+        <v>95177</v>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 11:59:45</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN58500CE</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25 12:11:54</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>404.8</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>316.01</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>402.19</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>316.01</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>1599.5</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>1549.5</v>
+      </c>
+      <c r="O121" s="2" t="n">
+        <v>12568.5</v>
+      </c>
+      <c r="P121" s="2" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="Q121" s="2" t="n">
+        <v>1599.5</v>
+      </c>
+      <c r="R121" s="2" t="n">
+        <v>-488.25</v>
+      </c>
+      <c r="S121" s="2" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="T121" s="2" t="n">
+        <v>-3.88</v>
+      </c>
+      <c r="U121" s="2" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="V121" s="2" t="n">
+        <v>96726.5</v>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 09:22:06</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN58100PE</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29 09:25:19</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>294.95</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>227.3</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>289.3</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>227.3</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>1282.75</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>1232.75</v>
+      </c>
+      <c r="O122" s="2" t="n">
+        <v>9040.5</v>
+      </c>
+      <c r="P122" s="2" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="Q122" s="2" t="n">
+        <v>1282.75</v>
+      </c>
+      <c r="R122" s="2" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="S122" s="2" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="T122" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="U122" s="2" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="V122" s="2" t="n">
+        <v>97959.25</v>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 09:20:02</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUN57800PE</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>171.35</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30 09:22:15</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>193.1</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>150.79</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>191.91</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>150.79</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>761.25</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>711.25</v>
+      </c>
+      <c r="O123" s="2" t="n">
+        <v>5997.25</v>
+      </c>
+      <c r="P123" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="Q123" s="2" t="n">
+        <v>761.25</v>
+      </c>
+      <c r="R123" s="2" t="n">
+        <v>-386.75</v>
+      </c>
+      <c r="S123" s="2" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="T123" s="2" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="U123" s="2" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="V123" s="2" t="n">
+        <v>98670.5</v>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 09:20:02</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57700CE</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>1200.15</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01 11:59:07</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>1288.35</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>1116.14</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>1284.16</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>1116.14</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>3087</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>3037</v>
+      </c>
+      <c r="O124" s="2" t="n">
+        <v>42005.25</v>
+      </c>
+      <c r="P124" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="Q124" s="2" t="n">
+        <v>3087</v>
+      </c>
+      <c r="R124" s="2" t="n">
+        <v>-1667.75</v>
+      </c>
+      <c r="S124" s="2" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="T124" s="2" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="U124" s="2" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="V124" s="2" t="n">
+        <v>101707.5</v>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:29:28</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL58100PE</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>790</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 11:38:42</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>845.6</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>734.7</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>845.3</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>734.7</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>1946</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>1896</v>
+      </c>
+      <c r="O125" s="2" t="n">
+        <v>27650</v>
+      </c>
+      <c r="P125" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="Q125" s="2" t="n">
+        <v>1946</v>
+      </c>
+      <c r="R125" s="2" t="n">
+        <v>-1004.5</v>
+      </c>
+      <c r="S125" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="T125" s="2" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="U125" s="2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V125" s="2" t="n">
+        <v>103603.5</v>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 09:20:02</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL58000PE</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>751.1</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:30:05</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>713</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>713.54</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>788.66</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>713.54</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1333.5</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-1383.5</v>
+      </c>
+      <c r="O126" s="2" t="n">
+        <v>26288.5</v>
+      </c>
+      <c r="P126" s="2" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="Q126" s="2" t="n">
+        <v>311.5</v>
+      </c>
+      <c r="R126" s="2" t="n">
+        <v>-1333.5</v>
+      </c>
+      <c r="S126" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T126" s="2" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="U126" s="2" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="V126" s="2" t="n">
+        <v>102220</v>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 09:23:03</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL58600CE</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>765.1</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07 09:34:47</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>726.4</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>726.85</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>803.36</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>726.85</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1354.5</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-1404.5</v>
+      </c>
+      <c r="O127" s="2" t="n">
+        <v>26778.5</v>
+      </c>
+      <c r="P127" s="2" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="Q127" s="2" t="n">
+        <v>694.75</v>
+      </c>
+      <c r="R127" s="2" t="n">
+        <v>-1354.5</v>
+      </c>
+      <c r="S127" s="2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T127" s="2" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="U127" s="2" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>100815.5</v>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:20:02</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57800PE</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>637.6</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:24:36</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>683.2</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>592.97</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>682.23</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>592.97</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>1596</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>1546</v>
+      </c>
+      <c r="O128" s="2" t="n">
+        <v>22316</v>
+      </c>
+      <c r="P128" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="Q128" s="2" t="n">
+        <v>1596</v>
+      </c>
+      <c r="R128" s="2" t="n">
+        <v>-518</v>
+      </c>
+      <c r="S128" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="T128" s="2" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="U128" s="2" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="V128" s="2" t="n">
+        <v>102361.5</v>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 09:20:02</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57200CE</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>973.85</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:28:05</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>905.5</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>905.6799999999999</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>1042.02</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>905.6799999999999</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-2392.25</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-2442.25</v>
+      </c>
+      <c r="O129" s="2" t="n">
+        <v>34084.75</v>
+      </c>
+      <c r="P129" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="Q129" s="2" t="n">
+        <v>1090.25</v>
+      </c>
+      <c r="R129" s="2" t="n">
+        <v>-2392.25</v>
+      </c>
+      <c r="S129" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T129" s="2" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="U129" s="2" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="V129" s="2" t="n">
+        <v>99919.25</v>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 09:20:04</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57800CE</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 09:47:50</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>895</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>776.55</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>893.45</v>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>776.55</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N130" s="2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="O130" s="2" t="n">
+        <v>29225</v>
+      </c>
+      <c r="P130" s="2" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="Q130" s="2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="R130" s="2" t="n">
+        <v>-974.75</v>
+      </c>
+      <c r="S130" s="2" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="T130" s="2" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="U130" s="2" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="V130" s="2" t="n">
+        <v>101969.25</v>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:20:02</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57700PE</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>670.65</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:35:05</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>719</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>623.7</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>717.6</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>623.7</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>1692.25</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>1642.25</v>
+      </c>
+      <c r="O131" s="2" t="n">
+        <v>23472.75</v>
+      </c>
+      <c r="P131" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="Q131" s="2" t="n">
+        <v>1692.25</v>
+      </c>
+      <c r="R131" s="2" t="n">
+        <v>-1221.5</v>
+      </c>
+      <c r="S131" s="2" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="T131" s="2" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="U131" s="2" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="V131" s="2" t="n">
+        <v>103611.5</v>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:20:02</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57900CE</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>711.85</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:21:43</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>767.65</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>662.02</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>761.6799999999999</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>662.02</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>1903</v>
+      </c>
+      <c r="O132" s="2" t="n">
+        <v>24914.75</v>
+      </c>
+      <c r="P132" s="2" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="Q132" s="2" t="n">
+        <v>1953</v>
+      </c>
+      <c r="R132" s="2" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="S132" s="2" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="T132" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="U132" s="2" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="V132" s="2" t="n">
+        <v>105514.5</v>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:30:18</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57700PE</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>589.05</v>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 10:26:54</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>633</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>547.8200000000001</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>630.28</v>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>547.8200000000001</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>1538.25</v>
+      </c>
+      <c r="N133" s="2" t="n">
+        <v>1488.25</v>
+      </c>
+      <c r="O133" s="2" t="n">
+        <v>20616.75</v>
+      </c>
+      <c r="P133" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="Q133" s="2" t="n">
+        <v>1538.25</v>
+      </c>
+      <c r="R133" s="2" t="n">
+        <v>-770</v>
+      </c>
+      <c r="S133" s="2" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="T133" s="2" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="U133" s="2" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="V133" s="2" t="n">
+        <v>107002.75</v>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:53:04</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57800CE</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>705.7</v>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:59:56</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>755.8</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>656.3</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>755.1</v>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>656.3</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>1753.5</v>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>1703.5</v>
+      </c>
+      <c r="O134" s="2" t="n">
+        <v>24699.5</v>
+      </c>
+      <c r="P134" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q134" s="2" t="n">
+        <v>1753.5</v>
+      </c>
+      <c r="R134" s="2" t="n">
+        <v>-143.5</v>
+      </c>
+      <c r="S134" s="2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="T134" s="2" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="U134" s="2" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="V134" s="2" t="n">
+        <v>108706.25</v>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 09:20:03</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57800PE</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>417</v>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21 12:30:24</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>366.35</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>366.96</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>467.04</v>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>366.96</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>-1772.75</v>
+      </c>
+      <c r="N135" s="2" t="n">
+        <v>-1822.75</v>
+      </c>
+      <c r="O135" s="2" t="n">
+        <v>14595</v>
+      </c>
+      <c r="P135" s="2" t="n">
+        <v>-12.15</v>
+      </c>
+      <c r="Q135" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="R135" s="2" t="n">
+        <v>-1772.75</v>
+      </c>
+      <c r="S135" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="T135" s="2" t="n">
+        <v>-12.15</v>
+      </c>
+      <c r="U135" s="2" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="V135" s="2" t="n">
+        <v>106883.5</v>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 09:30:57</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL57500PE</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>467.1</v>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 09:31:28</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>524.95</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>411.05</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>523.15</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>411.05</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>2024.75</v>
+      </c>
+      <c r="N136" s="2" t="n">
+        <v>1974.75</v>
+      </c>
+      <c r="O136" s="2" t="n">
+        <v>16348.5</v>
+      </c>
+      <c r="P136" s="2" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="Q136" s="2" t="n">
+        <v>2024.75</v>
+      </c>
+      <c r="R136" s="2" t="n">
+        <v>1268.75</v>
+      </c>
+      <c r="S136" s="2" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="T136" s="2" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="U136" s="2" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="V136" s="2" t="n">
+        <v>108858.25</v>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 09:20:03</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL56600PE</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>358.05</v>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23 12:30:51</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>403.95</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>315.08</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>401.02</v>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>315.08</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>1606.5</v>
+      </c>
+      <c r="N137" s="2" t="n">
+        <v>1556.5</v>
+      </c>
+      <c r="O137" s="2" t="n">
+        <v>12531.75</v>
+      </c>
+      <c r="P137" s="2" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="Q137" s="2" t="n">
+        <v>1606.5</v>
+      </c>
+      <c r="R137" s="2" t="n">
+        <v>-311.5</v>
+      </c>
+      <c r="S137" s="2" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="T137" s="2" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="U137" s="2" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="V137" s="2" t="n">
+        <v>110414.75</v>
+      </c>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:23:04</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL56100PE</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 11:20:40</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>281.2</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>283.32</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>283.32</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M138" s="2" t="n">
+        <v>-1426.25</v>
+      </c>
+      <c r="N138" s="2" t="n">
+        <v>-1476.25</v>
+      </c>
+      <c r="O138" s="2" t="n">
+        <v>11268.25</v>
+      </c>
+      <c r="P138" s="2" t="n">
+        <v>-12.66</v>
+      </c>
+      <c r="Q138" s="2" t="n">
+        <v>1296.75</v>
+      </c>
+      <c r="R138" s="2" t="n">
+        <v>-1426.25</v>
+      </c>
+      <c r="S138" s="2" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="T138" s="2" t="n">
+        <v>-12.66</v>
+      </c>
+      <c r="U138" s="2" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="V138" s="2" t="n">
+        <v>108938.5</v>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:20:03</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26JUL56900PE</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:55:56</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>140.01</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>178.19</v>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>140.01</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M139" s="2" t="n">
+        <v>-717.5</v>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>-767.5</v>
+      </c>
+      <c r="O139" s="2" t="n">
+        <v>5568.5</v>
+      </c>
+      <c r="P139" s="2" t="n">
+        <v>-12.88</v>
+      </c>
+      <c r="Q139" s="2" t="n">
+        <v>567</v>
+      </c>
+      <c r="R139" s="2" t="n">
+        <v>-717.5</v>
+      </c>
+      <c r="S139" s="2" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="T139" s="2" t="n">
+        <v>-12.88</v>
+      </c>
+      <c r="U139" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="V139" s="2" t="n">
+        <v>108171</v>
+      </c>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 09:45:27</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26AUG57800CE</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>762.9</v>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 10:31:48</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>816.9</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>709.5</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>816.3</v>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>709.5</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M140" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>1840</v>
+      </c>
+      <c r="O140" s="2" t="n">
+        <v>26701.5</v>
+      </c>
+      <c r="P140" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="Q140" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="R140" s="2" t="n">
+        <v>-61.25</v>
+      </c>
+      <c r="S140" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="T140" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="U140" s="2" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="V140" s="2" t="n">
+        <v>110011</v>
+      </c>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:20:03</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26AUG57800PE</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>574.95</v>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:31:55</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>615.85</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>534.7</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>534.7</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M141" s="2" t="n">
+        <v>1431.5</v>
+      </c>
+      <c r="N141" s="2" t="n">
+        <v>1381.5</v>
+      </c>
+      <c r="O141" s="2" t="n">
+        <v>20123.25</v>
+      </c>
+      <c r="P141" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="Q141" s="2" t="n">
+        <v>1431.5</v>
+      </c>
+      <c r="R141" s="2" t="n">
+        <v>-1141</v>
+      </c>
+      <c r="S141" s="2" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="T141" s="2" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="U141" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="V141" s="2" t="n">
+        <v>111392.5</v>
+      </c>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:20:03</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26AUG57800PE</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>541.7</v>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:25:21</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>581.45</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>503.78</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>579.62</v>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>503.78</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M142" s="2" t="n">
+        <v>1391.25</v>
+      </c>
+      <c r="N142" s="2" t="n">
+        <v>1341.25</v>
+      </c>
+      <c r="O142" s="2" t="n">
+        <v>18959.5</v>
+      </c>
+      <c r="P142" s="2" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="Q142" s="2" t="n">
+        <v>1391.25</v>
+      </c>
+      <c r="R142" s="2" t="n">
+        <v>-115.5</v>
+      </c>
+      <c r="S142" s="2" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="T142" s="2" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="U142" s="2" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="V142" s="2" t="n">
+        <v>112733.75</v>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:20:03</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>BANKNIFTY</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>NSE:BANKNIFTY26AUG57300PE</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>520.65</v>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:42:45</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>557.2</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>484.2</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>557.1</v>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>484.2</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>1279.25</v>
+      </c>
+      <c r="N143" s="2" t="n">
+        <v>1229.25</v>
+      </c>
+      <c r="O143" s="2" t="n">
+        <v>18222.75</v>
+      </c>
+      <c r="P143" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="Q143" s="2" t="n">
+        <v>1279.25</v>
+      </c>
+      <c r="R143" s="2" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="S143" s="2" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="T143" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="U143" s="2" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="V143" s="2" t="n">
+        <v>113963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
